--- a/data/trans_camb/IP07B_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP07B_R2-Edad-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -622,645 +631,617 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,57</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,28</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.813097414744301</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.567094472989518</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.283529482178588</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.7763501128363848</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.1253623201683346</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.762334745250815</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.293753474202008</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>-0.270908145060917</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>0.08219351748446797</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,91; 5,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,35; 2,34</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,51; 2,04</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,2; 3,41</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-3,04; 2,26</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-1,01; 7,05</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-1,14; 3,6</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-2,25; 1,66</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 2,9</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.914888324996518</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.348167026887214</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.506809213753499</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.202403568207519</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-3.04060253239987</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.012664424814577</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>-1.144440875415309</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>-2.249006863704064</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>-2.263162343340831</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>62,75%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-19,63%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-44,42%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>127,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>59,4%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-12,44%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.536472539136178</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>2.342635308535178</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.04106641209175</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.41293988744656</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>2.2573836856542</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>7.04805270079386</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>3.59612634697887</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>1.663103598180552</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>2.897826398530865</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-45,42; 468,97</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 343,81</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-41,83; 310,04</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-69,57; 161,92</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>-80,97; 303,29</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.6275288461026046</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1962763486243593</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.4442407607777629</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.5597090811085013</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.09037987870021191</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1.270554025253037</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.5939653546799813</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1243745857888832</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0.03773524302624167</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-2,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-0.4541720430489304</v>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="n">
+        <v>-0.4182747312446603</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6956904732293497</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-0.8097237862727117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,65; 4,02</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,99; 2,04</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,55; 2,58</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 4,98</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-3,52; 1,44</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-4,59; -0,56</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-0,45; 3,86</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-2,1; 1,08</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 0,82</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4.689713952614344</v>
+      </c>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="n">
+        <v>3.438084273973675</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="n">
+        <v>3.100419979527621</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.619176197263925</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>3.032937328951067</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>127,86%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-9,11%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,17%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>57,84%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-38,63%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-89,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>79,53%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-29,42%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-51,66%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1.509821299232377</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.1075425186802695</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1909019230052888</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.517401700797202</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.013450742076385</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-2.338642444074285</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>1.501755310409243</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>-0.5555058703570707</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-0.9754934371198154</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-51,52; 985,13</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-48,72; 382,12</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-89,54; 116,63</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 95,69</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-21,15; 341,63</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-76,44; 110,37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>-88,01; 160,9</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.6512766939312419</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.989679353527012</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.554971143378832</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.565560229220538</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-3.523184641669677</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-4.593860964585288</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>-0.4538881165270818</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>-2.103297676139666</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>-2.3776085678881</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,78</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,82</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-0,37</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.018792247904495</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.039358412419193</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.578199968807537</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.977544875654676</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.439555089892506</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-0.5617122687806647</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>3.855858515459423</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>1.081779475895631</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>0.8171132551647796</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,13; 4,19</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,9; 1,78</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,26; 1,42</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 3,4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,38; 1,09</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-2,7; 1,3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,03; 3,07</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-1,51; 0,94</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-1,88; 0,62</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1.278571478820317</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.09107090833531217</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.1616626776497394</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.5784391249961054</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3863311608029261</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.8914991253261265</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.7952585908583043</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.294169637764286</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>-0.516575190923762</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-8,77%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-21,87%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>48,82%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-27,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-38,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-18,59%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-29,88%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.5152421298897052</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="n">
+        <v>-0.4871896567971449</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.8954313509245059</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2114952608811512</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7643537341390099</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>-0.8801499554589352</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-17,51; 420,69</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-70,92; 220,32</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-84,51; 188,79</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-36,98; 264,52</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-77,52; 113,65</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-87,42; 128,63</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-4,07; 215,25</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-59,17; 83,19</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>-72,9; 45,62</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>9.851294101061628</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="n">
+        <v>3.821175116461659</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.166331888906196</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.9569096486280517</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>3.416285209019563</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.103650212265439</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>1.609010059721239</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>1.780911288557792</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.1635278260119409</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.4078830904833098</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.048985262971416</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.5905989586963329</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.817236939051509</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.426964009227748</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>-0.3722577239533231</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>-0.5982782449851102</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.1343577950548344</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.899506688760933</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.264233879842158</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.085487543326962</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-2.383753509371357</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-2.704657380981032</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0.02819189541900694</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>-1.513692785334954</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-1.880176491938823</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.185516453889713</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.775694895554047</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.422224300231673</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.399809300911978</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.091515519621714</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.301556634077195</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>3.066499223044747</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0.9430484761929657</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>0.6206089655377902</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.955063111198353</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.0876963357366012</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.2187386288722195</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.4882022070188876</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.2748672696143141</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.3803455504914738</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.7127393097941201</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.185935112252488</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>-0.298827735414501</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-0.1750973207034064</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.7091828092379091</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.8450765317736114</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.3697969735815389</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.775153301906536</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.874208865503423</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.04066466807638302</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>-0.5916649559770736</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>-0.7290238475442082</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>4.206946793371734</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>2.203191647073771</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1.887892425821165</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>2.645163148298336</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>1.136510681278721</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.286311845184492</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>2.152455063930724</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.831940949578176</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0.4562406080920124</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1268,12 +1249,12 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
